--- a/data/config/fundos_mapeamento.xlsx
+++ b/data/config/fundos_mapeamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Tesouraria\App Tesouraria Botuverá\Código\data\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CBD0DC-06EB-46F8-815A-59DA371FFA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAF23FD-B584-4757-9602-5A6AED361059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
   <si>
     <t>Fundo</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>D+31</t>
+  </si>
+  <si>
+    <t>D+6</t>
   </si>
 </sst>
 </file>
@@ -740,7 +743,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>44</v>
